--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D43A32-11DD-45FC-B176-3B870B91BB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E669F5FA-9EE7-441A-8205-73EE7ED5469B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="76">
   <si>
     <t>DATE</t>
   </si>
@@ -241,6 +241,28 @@
   </si>
   <si>
     <t>2. chatbots introduction</t>
+  </si>
+  <si>
+    <t>1. Project work</t>
+  </si>
+  <si>
+    <t>2. Mlops introduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.project work
+</t>
+  </si>
+  <si>
+    <t>2. dataiku download</t>
+  </si>
+  <si>
+    <t>1. java class on loops for,while,do-while</t>
+  </si>
+  <si>
+    <t>2. html audio code exwcution</t>
+  </si>
+  <si>
+    <t>3. dataiku tool  documentation on (home page options)</t>
   </si>
 </sst>
 </file>
@@ -297,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -315,14 +337,17 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -639,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -662,7 +687,7 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="A2" s="10">
         <v>45636</v>
       </c>
       <c r="B2" t="s">
@@ -679,7 +704,7 @@
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
+      <c r="A3" s="10"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -688,7 +713,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="10">
         <v>45637</v>
       </c>
       <c r="B4" t="s">
@@ -702,7 +727,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="10"/>
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -711,7 +736,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -723,7 +748,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>45638</v>
       </c>
       <c r="B7" t="s">
@@ -734,7 +759,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="10"/>
       <c r="B8" t="s">
         <v>13</v>
       </c>
@@ -743,7 +768,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
+      <c r="A9" s="10"/>
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -752,7 +777,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="10">
         <v>45639</v>
       </c>
       <c r="B10" t="s">
@@ -763,7 +788,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="10"/>
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -772,7 +797,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
+      <c r="A12" s="10"/>
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -797,7 +822,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>45642</v>
       </c>
       <c r="B15" t="s">
@@ -808,7 +833,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="10"/>
       <c r="B16" t="s">
         <v>22</v>
       </c>
@@ -817,7 +842,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
+      <c r="A17" s="10"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
@@ -826,7 +851,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>45643</v>
       </c>
       <c r="B18" t="s">
@@ -837,7 +862,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+      <c r="A19" s="10"/>
       <c r="B19" t="s">
         <v>25</v>
       </c>
@@ -846,7 +871,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
+      <c r="A20" s="10"/>
       <c r="B20" t="s">
         <v>26</v>
       </c>
@@ -855,7 +880,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>45644</v>
       </c>
       <c r="B21" t="s">
@@ -866,7 +891,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
+      <c r="A22" s="10"/>
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -875,7 +900,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
+      <c r="A23" s="10"/>
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -884,7 +909,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>45645</v>
       </c>
       <c r="B24" t="s">
@@ -895,7 +920,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
+      <c r="A25" s="10"/>
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -904,7 +929,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
+      <c r="A26" s="10"/>
       <c r="B26" t="s">
         <v>26</v>
       </c>
@@ -913,7 +938,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="9">
+      <c r="A27" s="10">
         <v>45646</v>
       </c>
       <c r="B27" t="s">
@@ -924,7 +949,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
+      <c r="A28" s="10"/>
       <c r="B28" t="s">
         <v>32</v>
       </c>
@@ -933,7 +958,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
+      <c r="A29" s="10"/>
       <c r="B29" t="s">
         <v>33</v>
       </c>
@@ -942,7 +967,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
+      <c r="A30" s="10"/>
       <c r="B30" t="s">
         <v>34</v>
       </c>
@@ -951,7 +976,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
+      <c r="A31" s="10"/>
       <c r="B31" t="s">
         <v>35</v>
       </c>
@@ -976,7 +1001,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
+      <c r="A34" s="12">
         <v>45649</v>
       </c>
       <c r="B34" t="s">
@@ -987,7 +1012,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
+      <c r="A35" s="12"/>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1121,7 +1146,7 @@
       <c r="A50" s="11"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <v>45660</v>
       </c>
       <c r="B51" t="s">
@@ -1132,7 +1157,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
+      <c r="A52" s="10"/>
       <c r="B52" t="s">
         <v>45</v>
       </c>
@@ -1157,7 +1182,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="9">
+      <c r="A55" s="10">
         <v>45663</v>
       </c>
       <c r="B55" t="s">
@@ -1168,7 +1193,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
+      <c r="A56" s="10"/>
       <c r="B56" t="s">
         <v>49</v>
       </c>
@@ -1177,7 +1202,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
+      <c r="A57" s="10"/>
       <c r="B57" t="s">
         <v>50</v>
       </c>
@@ -1186,7 +1211,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="9">
+      <c r="A58" s="10">
         <v>45664</v>
       </c>
       <c r="B58" t="s">
@@ -1197,7 +1222,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
+      <c r="A59" s="10"/>
       <c r="B59" t="s">
         <v>51</v>
       </c>
@@ -1206,7 +1231,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
+      <c r="A60" s="10"/>
       <c r="B60" t="s">
         <v>52</v>
       </c>
@@ -1215,7 +1240,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="9">
+      <c r="A61" s="10">
         <v>45665</v>
       </c>
       <c r="B61" t="s">
@@ -1226,7 +1251,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="9"/>
+      <c r="A62" s="10"/>
       <c r="B62" t="s">
         <v>54</v>
       </c>
@@ -1235,7 +1260,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
+      <c r="A63" s="10"/>
       <c r="B63" t="s">
         <v>55</v>
       </c>
@@ -1244,7 +1269,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
+      <c r="A64" s="10"/>
       <c r="B64" t="s">
         <v>56</v>
       </c>
@@ -1253,7 +1278,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
+      <c r="A65" s="10"/>
       <c r="B65" t="s">
         <v>57</v>
       </c>
@@ -1262,7 +1287,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="9">
+      <c r="A66" s="10">
         <v>45666</v>
       </c>
       <c r="B66" t="s">
@@ -1273,7 +1298,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
+      <c r="A67" s="10"/>
       <c r="B67" t="s">
         <v>59</v>
       </c>
@@ -1282,7 +1307,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
+      <c r="A68" s="10"/>
       <c r="B68" t="s">
         <v>60</v>
       </c>
@@ -1291,7 +1316,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
+      <c r="A69" s="10"/>
       <c r="B69" t="s">
         <v>61</v>
       </c>
@@ -1300,7 +1325,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="9"/>
+      <c r="A70" s="10"/>
       <c r="B70" t="s">
         <v>62</v>
       </c>
@@ -1309,7 +1334,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="9">
+      <c r="A71" s="10">
         <v>45667</v>
       </c>
       <c r="B71" t="s">
@@ -1320,7 +1345,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
+      <c r="A72" s="10"/>
       <c r="B72" t="s">
         <v>63</v>
       </c>
@@ -1329,7 +1354,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
+      <c r="A73" s="10"/>
       <c r="B73" t="s">
         <v>64</v>
       </c>
@@ -1338,7 +1363,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
+      <c r="A74" s="10"/>
       <c r="B74" t="s">
         <v>65</v>
       </c>
@@ -1347,7 +1372,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="9"/>
+      <c r="A75" s="10"/>
       <c r="B75" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1384,7 @@
       <c r="A76" s="1">
         <v>45668</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1367,7 +1392,7 @@
       <c r="A77" s="1">
         <v>45669</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1375,12 +1400,12 @@
       <c r="A78" s="1">
         <v>45670</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="9">
+      <c r="A79" s="10">
         <v>45671</v>
       </c>
       <c r="B79" t="s">
@@ -1391,7 +1416,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="9"/>
+      <c r="A80" s="10"/>
       <c r="B80" t="s">
         <v>68</v>
       </c>
@@ -1399,11 +1424,77 @@
         <v>6</v>
       </c>
     </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="10">
+        <v>45672</v>
+      </c>
+      <c r="B81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="10"/>
+      <c r="B82" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="10">
+        <v>45673</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="10"/>
+      <c r="B84" t="s">
+        <v>72</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="10">
+        <v>45674</v>
+      </c>
+      <c r="B85" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="10"/>
+      <c r="B86" t="s">
+        <v>74</v>
+      </c>
+      <c r="C86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="10"/>
+      <c r="B87" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A71:A75"/>
+  <mergeCells count="21">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -1414,11 +1505,17 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A71:A75"/>
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A58:A60"/>
     <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A85:A87"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E669F5FA-9EE7-441A-8205-73EE7ED5469B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87D6F36-8725-4B34-BDB8-80AEA84F3140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
   <si>
     <t>DATE</t>
   </si>
@@ -263,6 +263,27 @@
   </si>
   <si>
     <t>3. dataiku tool  documentation on (home page options)</t>
+  </si>
+  <si>
+    <t>project work</t>
+  </si>
+  <si>
+    <t>1.project work</t>
+  </si>
+  <si>
+    <t>2. dataiku recipes practice filter,gropu by, joints</t>
+  </si>
+  <si>
+    <t>3.java practice to team member on loop</t>
+  </si>
+  <si>
+    <t>1. project</t>
+  </si>
+  <si>
+    <t>2. sync, split recipe practice in dataiku</t>
+  </si>
+  <si>
+    <t>3. aws app config</t>
   </si>
 </sst>
 </file>
@@ -664,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -1493,8 +1514,78 @@
         <v>6</v>
       </c>
     </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45948</v>
+      </c>
+      <c r="B88" t="s">
+        <v>76</v>
+      </c>
+      <c r="C88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="10">
+        <v>45951</v>
+      </c>
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="10"/>
+      <c r="B90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="10"/>
+      <c r="B91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="10">
+        <v>45952</v>
+      </c>
+      <c r="B92" t="s">
+        <v>80</v>
+      </c>
+      <c r="C92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="10"/>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="10"/>
+      <c r="B94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -1505,6 +1596,8 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A89:A91"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="A81:A82"/>
@@ -1515,7 +1608,6 @@
     <mergeCell ref="A66:A70"/>
     <mergeCell ref="A58:A60"/>
     <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A85:A87"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87D6F36-8725-4B34-BDB8-80AEA84F3140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4276AB8F-D585-4138-8175-05122EF01205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
   <si>
     <t>DATE</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>3. aws app config</t>
+  </si>
+  <si>
+    <t>1. Project work
+2. Python recipe in dataiku
+3.  Structure of jinja2 files
+4.  App config in aws</t>
   </si>
 </sst>
 </file>
@@ -340,7 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -365,10 +371,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -685,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -1022,7 +1031,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
+      <c r="A34" s="11">
         <v>45649</v>
       </c>
       <c r="B34" t="s">
@@ -1033,7 +1042,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
+      <c r="A35" s="11"/>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1117,7 +1126,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="11">
+      <c r="A45" s="12">
         <v>45659</v>
       </c>
       <c r="B45" t="s">
@@ -1128,7 +1137,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
+      <c r="A46" s="12"/>
       <c r="B46" s="7" t="s">
         <v>41</v>
       </c>
@@ -1137,7 +1146,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
+      <c r="A47" s="12"/>
       <c r="B47" s="7" t="s">
         <v>42</v>
       </c>
@@ -1146,7 +1155,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
+      <c r="A48" s="12"/>
       <c r="B48" t="s">
         <v>43</v>
       </c>
@@ -1155,7 +1164,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
+      <c r="A49" s="12"/>
       <c r="B49" t="s">
         <v>44</v>
       </c>
@@ -1164,7 +1173,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
+      <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
@@ -1583,8 +1592,33 @@
         <v>6</v>
       </c>
     </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="10">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="10"/>
+      <c r="B96" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A66:A70"/>
     <mergeCell ref="A92:A94"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
@@ -1601,13 +1635,6 @@
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A55:A57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4276AB8F-D585-4138-8175-05122EF01205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91C9EAD-0249-44A4-8FF3-7B23499C6BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="90">
   <si>
     <t>DATE</t>
   </si>
@@ -290,6 +290,27 @@
 2. Python recipe in dataiku
 3.  Structure of jinja2 files
 4.  App config in aws</t>
+  </si>
+  <si>
+    <t>1. Project work
+2. Python recipe in dataiku 
+3.  Structure of jinja2 files
+4.  App config in aws"</t>
+  </si>
+  <si>
+    <t>2. jinja template code understanding</t>
+  </si>
+  <si>
+    <t>3. project flow understanding</t>
+  </si>
+  <si>
+    <t>2.app config</t>
+  </si>
+  <si>
+    <t>3. event bridge-&gt;sqs-&gt;app config-&gt;dataiku flow understanding</t>
+  </si>
+  <si>
+    <t>2.python recipe code for jinjatemplates</t>
   </si>
 </sst>
 </file>
@@ -346,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -367,6 +388,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -376,9 +400,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -694,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -717,7 +739,7 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+      <c r="A2" s="11">
         <v>45636</v>
       </c>
       <c r="B2" t="s">
@@ -734,7 +756,7 @@
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="10"/>
+      <c r="A3" s="11"/>
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -743,7 +765,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>45637</v>
       </c>
       <c r="B4" t="s">
@@ -757,7 +779,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
+      <c r="A5" s="11"/>
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -766,7 +788,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -778,7 +800,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>45638</v>
       </c>
       <c r="B7" t="s">
@@ -789,7 +811,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="11"/>
       <c r="B8" t="s">
         <v>13</v>
       </c>
@@ -798,7 +820,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="11"/>
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -807,7 +829,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>45639</v>
       </c>
       <c r="B10" t="s">
@@ -818,7 +840,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="11"/>
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -827,7 +849,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="11"/>
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -852,7 +874,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <v>45642</v>
       </c>
       <c r="B15" t="s">
@@ -863,7 +885,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="11"/>
       <c r="B16" t="s">
         <v>22</v>
       </c>
@@ -872,7 +894,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
+      <c r="A17" s="11"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
@@ -881,7 +903,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <v>45643</v>
       </c>
       <c r="B18" t="s">
@@ -892,7 +914,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+      <c r="A19" s="11"/>
       <c r="B19" t="s">
         <v>25</v>
       </c>
@@ -901,7 +923,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
+      <c r="A20" s="11"/>
       <c r="B20" t="s">
         <v>26</v>
       </c>
@@ -910,7 +932,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <v>45644</v>
       </c>
       <c r="B21" t="s">
@@ -921,7 +943,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
+      <c r="A22" s="11"/>
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -930,7 +952,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="A23" s="11"/>
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -939,7 +961,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <v>45645</v>
       </c>
       <c r="B24" t="s">
@@ -950,7 +972,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
+      <c r="A25" s="11"/>
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -959,7 +981,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="11"/>
       <c r="B26" t="s">
         <v>26</v>
       </c>
@@ -968,7 +990,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <v>45646</v>
       </c>
       <c r="B27" t="s">
@@ -979,7 +1001,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
+      <c r="A28" s="11"/>
       <c r="B28" t="s">
         <v>32</v>
       </c>
@@ -988,7 +1010,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="10"/>
+      <c r="A29" s="11"/>
       <c r="B29" t="s">
         <v>33</v>
       </c>
@@ -997,7 +1019,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
+      <c r="A30" s="11"/>
       <c r="B30" t="s">
         <v>34</v>
       </c>
@@ -1006,7 +1028,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="10"/>
+      <c r="A31" s="11"/>
       <c r="B31" t="s">
         <v>35</v>
       </c>
@@ -1031,7 +1053,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
+      <c r="A34" s="12">
         <v>45649</v>
       </c>
       <c r="B34" t="s">
@@ -1042,7 +1064,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
+      <c r="A35" s="12"/>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1126,7 +1148,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="12">
+      <c r="A45" s="13">
         <v>45659</v>
       </c>
       <c r="B45" t="s">
@@ -1137,7 +1159,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
+      <c r="A46" s="13"/>
       <c r="B46" s="7" t="s">
         <v>41</v>
       </c>
@@ -1146,7 +1168,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
       <c r="B47" s="7" t="s">
         <v>42</v>
       </c>
@@ -1155,7 +1177,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
       <c r="B48" t="s">
         <v>43</v>
       </c>
@@ -1164,7 +1186,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
       <c r="B49" t="s">
         <v>44</v>
       </c>
@@ -1173,10 +1195,10 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
+      <c r="A50" s="13"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="10">
+      <c r="A51" s="11">
         <v>45660</v>
       </c>
       <c r="B51" t="s">
@@ -1187,7 +1209,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
+      <c r="A52" s="11"/>
       <c r="B52" t="s">
         <v>45</v>
       </c>
@@ -1212,7 +1234,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="10">
+      <c r="A55" s="11">
         <v>45663</v>
       </c>
       <c r="B55" t="s">
@@ -1223,7 +1245,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="10"/>
+      <c r="A56" s="11"/>
       <c r="B56" t="s">
         <v>49</v>
       </c>
@@ -1232,7 +1254,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
+      <c r="A57" s="11"/>
       <c r="B57" t="s">
         <v>50</v>
       </c>
@@ -1241,7 +1263,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="10">
+      <c r="A58" s="11">
         <v>45664</v>
       </c>
       <c r="B58" t="s">
@@ -1252,7 +1274,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="10"/>
+      <c r="A59" s="11"/>
       <c r="B59" t="s">
         <v>51</v>
       </c>
@@ -1261,7 +1283,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
+      <c r="A60" s="11"/>
       <c r="B60" t="s">
         <v>52</v>
       </c>
@@ -1270,7 +1292,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="10">
+      <c r="A61" s="11">
         <v>45665</v>
       </c>
       <c r="B61" t="s">
@@ -1281,7 +1303,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="10"/>
+      <c r="A62" s="11"/>
       <c r="B62" t="s">
         <v>54</v>
       </c>
@@ -1290,7 +1312,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="10"/>
+      <c r="A63" s="11"/>
       <c r="B63" t="s">
         <v>55</v>
       </c>
@@ -1299,7 +1321,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="10"/>
+      <c r="A64" s="11"/>
       <c r="B64" t="s">
         <v>56</v>
       </c>
@@ -1308,7 +1330,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="10"/>
+      <c r="A65" s="11"/>
       <c r="B65" t="s">
         <v>57</v>
       </c>
@@ -1317,7 +1339,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="10">
+      <c r="A66" s="11">
         <v>45666</v>
       </c>
       <c r="B66" t="s">
@@ -1328,7 +1350,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="10"/>
+      <c r="A67" s="11"/>
       <c r="B67" t="s">
         <v>59</v>
       </c>
@@ -1337,7 +1359,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="10"/>
+      <c r="A68" s="11"/>
       <c r="B68" t="s">
         <v>60</v>
       </c>
@@ -1346,7 +1368,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="10"/>
+      <c r="A69" s="11"/>
       <c r="B69" t="s">
         <v>61</v>
       </c>
@@ -1355,7 +1377,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="10"/>
+      <c r="A70" s="11"/>
       <c r="B70" t="s">
         <v>62</v>
       </c>
@@ -1364,7 +1386,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="10">
+      <c r="A71" s="11">
         <v>45667</v>
       </c>
       <c r="B71" t="s">
@@ -1375,7 +1397,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="10"/>
+      <c r="A72" s="11"/>
       <c r="B72" t="s">
         <v>63</v>
       </c>
@@ -1384,7 +1406,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="10"/>
+      <c r="A73" s="11"/>
       <c r="B73" t="s">
         <v>64</v>
       </c>
@@ -1393,7 +1415,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="10"/>
+      <c r="A74" s="11"/>
       <c r="B74" t="s">
         <v>65</v>
       </c>
@@ -1402,7 +1424,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="10"/>
+      <c r="A75" s="11"/>
       <c r="B75" t="s">
         <v>66</v>
       </c>
@@ -1435,7 +1457,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="10">
+      <c r="A79" s="11">
         <v>45671</v>
       </c>
       <c r="B79" t="s">
@@ -1446,7 +1468,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="10"/>
+      <c r="A80" s="11"/>
       <c r="B80" t="s">
         <v>68</v>
       </c>
@@ -1455,7 +1477,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="10">
+      <c r="A81" s="11">
         <v>45672</v>
       </c>
       <c r="B81" t="s">
@@ -1466,7 +1488,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="10"/>
+      <c r="A82" s="11"/>
       <c r="B82" t="s">
         <v>70</v>
       </c>
@@ -1475,7 +1497,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="10">
+      <c r="A83" s="11">
         <v>45673</v>
       </c>
       <c r="B83" s="9" t="s">
@@ -1486,7 +1508,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="10"/>
+      <c r="A84" s="11"/>
       <c r="B84" t="s">
         <v>72</v>
       </c>
@@ -1495,7 +1517,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="10">
+      <c r="A85" s="11">
         <v>45674</v>
       </c>
       <c r="B85" t="s">
@@ -1506,7 +1528,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="10"/>
+      <c r="A86" s="11"/>
       <c r="B86" t="s">
         <v>74</v>
       </c>
@@ -1515,7 +1537,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="10"/>
+      <c r="A87" s="11"/>
       <c r="B87" t="s">
         <v>75</v>
       </c>
@@ -1535,7 +1557,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="10">
+      <c r="A89" s="11">
         <v>45951</v>
       </c>
       <c r="B89" t="s">
@@ -1546,7 +1568,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="10"/>
+      <c r="A90" s="11"/>
       <c r="B90" t="s">
         <v>78</v>
       </c>
@@ -1555,7 +1577,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="10"/>
+      <c r="A91" s="11"/>
       <c r="B91" t="s">
         <v>79</v>
       </c>
@@ -1564,7 +1586,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="10">
+      <c r="A92" s="11">
         <v>45952</v>
       </c>
       <c r="B92" t="s">
@@ -1575,7 +1597,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="10"/>
+      <c r="A93" s="11"/>
       <c r="B93" t="s">
         <v>81</v>
       </c>
@@ -1584,7 +1606,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="10"/>
+      <c r="A94" s="11"/>
       <c r="B94" t="s">
         <v>82</v>
       </c>
@@ -1593,33 +1615,95 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="10">
+      <c r="A95" s="14"/>
+    </row>
+    <row r="96" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="14">
         <v>45953</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="10"/>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>83</v>
       </c>
       <c r="C96" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="10"/>
+    <row r="97" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="14">
+        <v>45954</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="11">
+        <v>45955</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="11"/>
+      <c r="B99" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="11"/>
+      <c r="B100" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
+        <v>45956</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="11"/>
+      <c r="B102" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="11"/>
+      <c r="B103" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="11">
+        <v>45957</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="11"/>
+      <c r="B105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="11"/>
+      <c r="B106" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="A92:A94"/>
+  <mergeCells count="26">
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -1630,11 +1714,16 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A85:A87"/>
     <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="A81:A82"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91C9EAD-0249-44A4-8FF3-7B23499C6BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB1A4B6-EEDB-4DF0-8B7D-ED4AC164F5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="94">
   <si>
     <t>DATE</t>
   </si>
@@ -311,6 +311,18 @@
   </si>
   <si>
     <t>2.python recipe code for jinjatemplates</t>
+  </si>
+  <si>
+    <t>2. jinja2 module installation in dataiku and error debudding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. exploration on basic packages to run python recipe </t>
+  </si>
+  <si>
+    <t>2. dataiku flow understanding, terraform code understanding</t>
+  </si>
+  <si>
+    <t>3. gen AI LLM - introduction</t>
   </si>
 </sst>
 </file>
@@ -367,7 +379,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -395,12 +407,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -716,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -1053,7 +1064,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>45649</v>
       </c>
       <c r="B34" t="s">
@@ -1064,7 +1075,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1148,7 +1159,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="13">
+      <c r="A45" s="12">
         <v>45659</v>
       </c>
       <c r="B45" t="s">
@@ -1159,7 +1170,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
+      <c r="A46" s="12"/>
       <c r="B46" s="7" t="s">
         <v>41</v>
       </c>
@@ -1168,7 +1179,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
+      <c r="A47" s="12"/>
       <c r="B47" s="7" t="s">
         <v>42</v>
       </c>
@@ -1177,7 +1188,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
+      <c r="A48" s="12"/>
       <c r="B48" t="s">
         <v>43</v>
       </c>
@@ -1186,7 +1197,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
+      <c r="A49" s="12"/>
       <c r="B49" t="s">
         <v>44</v>
       </c>
@@ -1195,7 +1206,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
+      <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
@@ -1615,10 +1626,10 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="14"/>
+      <c r="A95" s="1"/>
     </row>
     <row r="96" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="14">
+      <c r="A96" s="1">
         <v>45953</v>
       </c>
       <c r="B96" s="10" t="s">
@@ -1629,7 +1640,7 @@
       </c>
     </row>
     <row r="97" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A97" s="14">
+      <c r="A97" s="1">
         <v>45954</v>
       </c>
       <c r="B97" s="10" t="s">
@@ -1696,14 +1707,50 @@
         <v>88</v>
       </c>
     </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="11">
+        <v>45958</v>
+      </c>
+      <c r="B107" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="11"/>
+      <c r="B108" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="11"/>
+      <c r="B109" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="11">
+        <v>45959</v>
+      </c>
+      <c r="B110" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="11"/>
+      <c r="B111" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="11"/>
+      <c r="B112" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
+  <mergeCells count="28">
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -1714,6 +1761,12 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
     <mergeCell ref="A58:A60"/>
     <mergeCell ref="A55:A57"/>
     <mergeCell ref="A83:A84"/>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB1A4B6-EEDB-4DF0-8B7D-ED4AC164F5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613EF653-BA23-49B8-8506-57850E273688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="100">
   <si>
     <t>DATE</t>
   </si>
@@ -323,6 +323,24 @@
   </si>
   <si>
     <t>3. gen AI LLM - introduction</t>
+  </si>
+  <si>
+    <t>1. transformer models</t>
+  </si>
+  <si>
+    <t>2. context of large langauge models</t>
+  </si>
+  <si>
+    <t>3. Tableau and document preparation class</t>
+  </si>
+  <si>
+    <t>4. team disscussion on github</t>
+  </si>
+  <si>
+    <t>2. dataiku error debugging</t>
+  </si>
+  <si>
+    <t>3. transformer in LLM</t>
   </si>
 </sst>
 </file>
@@ -407,10 +425,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -727,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60.5546875" customWidth="1"/>
@@ -1064,7 +1082,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+      <c r="A34" s="12">
         <v>45649</v>
       </c>
       <c r="B34" t="s">
@@ -1075,7 +1093,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="12"/>
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -1159,7 +1177,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="12">
+      <c r="A45" s="13">
         <v>45659</v>
       </c>
       <c r="B45" t="s">
@@ -1170,7 +1188,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
+      <c r="A46" s="13"/>
       <c r="B46" s="7" t="s">
         <v>41</v>
       </c>
@@ -1179,7 +1197,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
       <c r="B47" s="7" t="s">
         <v>42</v>
       </c>
@@ -1188,7 +1206,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
       <c r="B48" t="s">
         <v>43</v>
       </c>
@@ -1197,7 +1215,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
       <c r="B49" t="s">
         <v>44</v>
       </c>
@@ -1206,7 +1224,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
+      <c r="A50" s="13"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
@@ -1747,8 +1765,68 @@
         <v>91</v>
       </c>
     </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="11">
+        <v>45960</v>
+      </c>
+      <c r="B113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="11"/>
+      <c r="B114" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="11"/>
+      <c r="B115" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="11">
+        <v>45961</v>
+      </c>
+      <c r="B116" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="11"/>
+      <c r="B117" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="11"/>
+      <c r="B118" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="11"/>
+      <c r="B119" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="30">
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A89:A91"/>
     <mergeCell ref="A107:A109"/>
     <mergeCell ref="A110:A112"/>
     <mergeCell ref="A2:A3"/>
@@ -1765,18 +1843,6 @@
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="A89:A91"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/daily_status/rahamatha_daily_tasks.xlsx
+++ b/daily_status/rahamatha_daily_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rahamatha_git\Daily_tasks\daily_status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613EF653-BA23-49B8-8506-57850E273688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DC73DF-86FE-42D2-BB5C-30042165D109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28A87E2F-8FA9-4910-ADA0-D5E070841179}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="101">
   <si>
     <t>DATE</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>3. transformer in LLM</t>
+  </si>
+  <si>
+    <t>2.Extract jinja templates files data into JSON files and combine all together</t>
   </si>
 </sst>
 </file>
@@ -745,10 +748,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03293BF-1487-4800-AFEB-EA441312AA74}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultColWidth="24.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="60.5546875" customWidth="1"/>
+    <col min="2" max="2" width="66.88671875" customWidth="1"/>
     <col min="4" max="4" width="95.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1811,24 +1814,41 @@
         <v>97</v>
       </c>
     </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45932</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="11">
+        <v>45934</v>
+      </c>
+      <c r="B123" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="11"/>
+      <c r="B124" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="A116:A119"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A112"/>
+  <mergeCells count="31">
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A123:A124"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -1839,10 +1859,23 @@
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="A116:A119"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A112"/>
     <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="A81:A82"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
